--- a/Laska_etal_2003/Laska_etal_2003_registry_rows.xlsx
+++ b/Laska_etal_2003/Laska_etal_2003_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R8687852dfb9c40fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Rcafd992deb5a476c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R4797a677a5cb472f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Ra3d2f44816d94325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R6a40a8855c10429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R7ed13ca6c1c144ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Acceptance and preference for citric-acid/sucrose mixtures</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Source tables / results to select</x:v>
+        <x:v>Table 1: Sucrose concentrations required for preference over a reference in acid–sugar mixtures</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — optional taste extension; gap required
@@ -350,13 +350,13 @@
         <x:v>Source citation and endpoint in existing source notes; Nick/Fran dissertation reference check.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 7 / printed p. 2643. Preserve citric-acid concentration, 50 mM sucrose reference and censored &gt;1000 value. These are mixture-preference thresholds, not pure-acid detection thresholds.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/3172685921/Laska-2003-Sour-taste-tolerance-in-four-specie.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,13 +508,15 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Laska, M., Scheuber, H.-P., Hernandez Salazar, L. T., &amp; Rodriguez Luna, E. (2003). Sour-taste tolerance in four species of nonhuman primates. Journal of Chemical Ecology, 29, 2637–2649. https://doi.org/10.1023/B:JOEC.0000008009.85523.7a</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Table 1</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Assistant addition; not found in dissertation references. Planned folder: Laska_etal_2003. Target: Source tables / results to select. Four primate species. This is mixture tolerance/preference, not a pure acid detection threshold. Retain both acid and sugar concentrations.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 7 / printed p. 2643. Preserve citric-acid concentration, 50 mM sucrose reference and censored &gt;1000 value. These are mixture-preference thresholds, not pure-acid detection thresholds. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/3172685921/Laska-2003-Sour-taste-tolerance-in-four-specie.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — optional taste extension; gap required</x:v>
@@ -550,7 +552,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Acceptance and preference for citric-acid/sucrose mixtures</x:v>
+        <x:v>Sucrose concentrations required for preference over a reference in acid–sugar mixtures</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -695,7 +697,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="100" customHeight="1">
@@ -703,7 +705,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -987,13 +989,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ADFF032-D34C-4034-9CF7-3C8FC9E9B381}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EFE4638-7CAF-439C-97D2-5BE12AB477F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C291B5-F974-4149-8E0C-DADB0683C9DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16024EC-3579-4D2D-9F22-490EB5BDF7FE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F919769-8870-4736-AC9F-A5488562232C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54D70177-E1E8-4738-A9D0-F8360E4BE23C}"/>
 </file>